--- a/InputData/elec/BDTPTUMCF/Boolean Does This Plant Type Use Maximum Capacity Factor.xlsx
+++ b/InputData/elec/BDTPTUMCF/Boolean Does This Plant Type Use Maximum Capacity Factor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\OR\elec\BDTPTUMCF\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OliviaAshmoore\Documents\Github Repos\state-eps-data\OR\elec\BDTPTUMCF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4FEF178E-AC68-4F8E-A361-CC3B82923459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DFC065AA-B1AB-4045-A3C7-6FE67F25AC8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1365" yWindow="1890" windowWidth="14700" windowHeight="12645" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="12" r:id="rId1"/>
@@ -369,6 +369,9 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Header Descriptions"/>
       <sheetName val="2019 NQC List"/>
@@ -390,6 +393,9 @@
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Information"/>
       <sheetName val="Request Type 1-2"/>
@@ -760,15 +766,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" customWidth="1"/>
-    <col min="2" max="2" width="50.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="49.5703125" customWidth="1"/>
-    <col min="8" max="8" width="53.7109375" customWidth="1"/>
+    <col min="1" max="1" width="9.265625" customWidth="1"/>
+    <col min="2" max="2" width="50.73046875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="49.59765625" customWidth="1"/>
+    <col min="8" max="8" width="53.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>25</v>
       </c>
@@ -776,13 +782,13 @@
         <v>33</v>
       </c>
       <c r="C1" s="11">
-        <v>45484</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+        <v>46184</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="G2" s="2"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -792,34 +798,34 @@
       <c r="E3" s="1"/>
       <c r="H3" s="1"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="H4" s="2"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
       <c r="H5" s="2"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>21</v>
       </c>
       <c r="H6" s="2"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>22</v>
       </c>
       <c r="H7" s="4"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>23</v>
       </c>
       <c r="H8" s="2"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -841,20 +847,20 @@
     <tabColor rgb="FF002060"/>
   </sheetPr>
   <dimension ref="A1:C25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="35.5703125" customWidth="1"/>
+    <col min="1" max="1" width="35.59765625" customWidth="1"/>
     <col min="2" max="3" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A1" s="6" t="s">
         <v>17</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="7"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -863,7 +869,7 @@
       </c>
       <c r="C2" s="3"/>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -872,7 +878,7 @@
       </c>
       <c r="C3" s="3"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -881,7 +887,7 @@
       </c>
       <c r="C4" s="3"/>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -890,7 +896,7 @@
       </c>
       <c r="C5" s="3"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -899,7 +905,7 @@
       </c>
       <c r="C6" s="3"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -908,7 +914,7 @@
       </c>
       <c r="C7" s="3"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -917,7 +923,7 @@
       </c>
       <c r="C8" s="3"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -926,7 +932,7 @@
       </c>
       <c r="C9" s="3"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -935,7 +941,7 @@
       </c>
       <c r="C10" s="3"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -944,7 +950,7 @@
       </c>
       <c r="C11" s="3"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -953,7 +959,7 @@
       </c>
       <c r="C12" s="3"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>0</v>
       </c>
@@ -962,7 +968,7 @@
       </c>
       <c r="C13" s="3"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -971,7 +977,7 @@
       </c>
       <c r="C14" s="3"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -980,7 +986,7 @@
       </c>
       <c r="C15" s="3"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -989,7 +995,7 @@
       </c>
       <c r="C16" s="3"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -998,7 +1004,7 @@
       </c>
       <c r="C17" s="3"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -1007,7 +1013,7 @@
       </c>
       <c r="C18" s="3"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -1016,7 +1022,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -1025,7 +1031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -1034,7 +1040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>29</v>
       </c>
@@ -1043,7 +1049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -1052,7 +1058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A24" s="10" t="s">
         <v>31</v>
       </c>
@@ -1060,7 +1066,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A25" s="10" t="s">
         <v>32</v>
       </c>
